--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MISSISSIPPI_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/MISSISSIPPI_2016.xlsx
@@ -499,7 +499,7 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="9">
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="20">
@@ -895,7 +895,7 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="31">
@@ -1075,7 +1075,7 @@
         <v>2</v>
       </c>
       <c r="D40">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="41">
@@ -1129,7 +1129,7 @@
         <v>2</v>
       </c>
       <c r="D43">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="44">
@@ -1147,7 +1147,7 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="45">
@@ -1399,7 +1399,7 @@
         <v>2</v>
       </c>
       <c r="D58">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="59">
@@ -1453,7 +1453,7 @@
         <v>2</v>
       </c>
       <c r="D61">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="62">
@@ -1561,7 +1561,7 @@
         <v>2</v>
       </c>
       <c r="D67">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="68">
@@ -1597,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="D69">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="70">
@@ -1633,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="D71">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="72">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C75">
@@ -1831,7 +1831,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="83">
@@ -2119,7 +2119,7 @@
         <v>2</v>
       </c>
       <c r="D98">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="99">
@@ -2281,7 +2281,7 @@
         <v>2</v>
       </c>
       <c r="D107">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="108">
@@ -2353,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="D111">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="112">
@@ -2371,7 +2371,7 @@
         <v>2</v>
       </c>
       <c r="D112">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="113">
@@ -2443,7 +2443,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="117">
@@ -2641,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="D127">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="128">
@@ -2713,7 +2713,7 @@
         <v>2</v>
       </c>
       <c r="D131">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="132">
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="D138">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="139">
@@ -2857,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="D139">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="140">
@@ -2875,7 +2875,7 @@
         <v>2</v>
       </c>
       <c r="D140">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="141">
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="150">
@@ -3073,7 +3073,7 @@
         <v>2</v>
       </c>
       <c r="D151">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="152">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C152">
@@ -3145,7 +3145,7 @@
         <v>2</v>
       </c>
       <c r="D155">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="156">
@@ -3235,7 +3235,7 @@
         <v>2</v>
       </c>
       <c r="D160">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="161">
@@ -3289,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="D163">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="164">
@@ -3361,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="D167">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="168">
@@ -3595,7 +3595,7 @@
         <v>2</v>
       </c>
       <c r="D180">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="181">
@@ -3649,7 +3649,7 @@
         <v>2</v>
       </c>
       <c r="D183">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="184">
@@ -3739,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="D188">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="189">
@@ -3757,7 +3757,7 @@
         <v>2</v>
       </c>
       <c r="D189">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="190">
@@ -3811,7 +3811,7 @@
         <v>2</v>
       </c>
       <c r="D192">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="193">
@@ -3829,7 +3829,7 @@
         <v>2</v>
       </c>
       <c r="D193">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="194">
@@ -3955,7 +3955,7 @@
         <v>2</v>
       </c>
       <c r="D200">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="201">
@@ -3973,7 +3973,7 @@
         <v>2</v>
       </c>
       <c r="D201">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="202">
@@ -4063,7 +4063,7 @@
         <v>2</v>
       </c>
       <c r="D206">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="207">
@@ -4261,7 +4261,7 @@
         <v>2</v>
       </c>
       <c r="D217">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="218">
@@ -4333,7 +4333,7 @@
         <v>2</v>
       </c>
       <c r="D221">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="222">
@@ -4351,7 +4351,7 @@
         <v>2</v>
       </c>
       <c r="D222">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="223">
@@ -4387,7 +4387,7 @@
         <v>2</v>
       </c>
       <c r="D224">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="225">
@@ -4477,7 +4477,7 @@
         <v>2</v>
       </c>
       <c r="D229">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="230">
@@ -4729,7 +4729,7 @@
         <v>2</v>
       </c>
       <c r="D243">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="244">
@@ -4765,7 +4765,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="246">
@@ -4999,7 +4999,7 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="259">
@@ -5179,7 +5179,7 @@
         <v>2</v>
       </c>
       <c r="D268">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="269">
@@ -5215,7 +5215,7 @@
         <v>2</v>
       </c>
       <c r="D270">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="271">
@@ -5233,7 +5233,7 @@
         <v>2</v>
       </c>
       <c r="D271">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="272">
@@ -5305,7 +5305,7 @@
         <v>2</v>
       </c>
       <c r="D275">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="276">
@@ -5431,7 +5431,7 @@
         <v>2</v>
       </c>
       <c r="D282">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="283">
@@ -5467,7 +5467,7 @@
         <v>2</v>
       </c>
       <c r="D284">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="285">
@@ -5629,7 +5629,7 @@
         <v>2</v>
       </c>
       <c r="D293">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="294">
@@ -5683,7 +5683,7 @@
         <v>2</v>
       </c>
       <c r="D296">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="297">
@@ -5737,7 +5737,7 @@
         <v>2</v>
       </c>
       <c r="D299">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="300">
@@ -5755,7 +5755,7 @@
         <v>2</v>
       </c>
       <c r="D300">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="301">
@@ -6043,7 +6043,7 @@
         <v>2</v>
       </c>
       <c r="D316">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="317">
@@ -6061,7 +6061,7 @@
         <v>2</v>
       </c>
       <c r="D317">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="318">
@@ -6115,7 +6115,7 @@
         <v>2</v>
       </c>
       <c r="D320">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="321">
@@ -6151,7 +6151,7 @@
         <v>2</v>
       </c>
       <c r="D322">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="323">
@@ -6187,7 +6187,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="325">
@@ -6241,7 +6241,7 @@
         <v>2</v>
       </c>
       <c r="D327">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="328">
@@ -6295,7 +6295,7 @@
         <v>2</v>
       </c>
       <c r="D330">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="331">
@@ -6331,7 +6331,7 @@
         <v>2</v>
       </c>
       <c r="D332">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="333">
@@ -6349,7 +6349,7 @@
         <v>2</v>
       </c>
       <c r="D333">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="334">
@@ -6403,7 +6403,7 @@
         <v>2</v>
       </c>
       <c r="D336">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="337">
@@ -6421,7 +6421,7 @@
         <v>2</v>
       </c>
       <c r="D337">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="338">
@@ -6457,7 +6457,7 @@
         <v>2</v>
       </c>
       <c r="D339">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="340">
@@ -6475,7 +6475,7 @@
         <v>2</v>
       </c>
       <c r="D340">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="341">
@@ -6493,7 +6493,7 @@
         <v>2</v>
       </c>
       <c r="D341">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="342">
@@ -6511,7 +6511,7 @@
         <v>2</v>
       </c>
       <c r="D342">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="343">
@@ -6547,7 +6547,7 @@
         <v>2</v>
       </c>
       <c r="D344">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="345">
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="D347">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="348">
@@ -6655,7 +6655,7 @@
         <v>2</v>
       </c>
       <c r="D350">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="351">
@@ -6781,7 +6781,7 @@
         <v>2</v>
       </c>
       <c r="D357">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="358">
@@ -6853,7 +6853,7 @@
         <v>2</v>
       </c>
       <c r="D361">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="362">
@@ -6925,7 +6925,7 @@
         <v>2</v>
       </c>
       <c r="D365">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="366">
@@ -6961,7 +6961,7 @@
         <v>2</v>
       </c>
       <c r="D367">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="368">
@@ -7033,7 +7033,7 @@
         <v>2</v>
       </c>
       <c r="D371">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="372">
@@ -7123,7 +7123,7 @@
         <v>2</v>
       </c>
       <c r="D376">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="377">
@@ -7231,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="D382">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="383">
@@ -7303,7 +7303,7 @@
         <v>2</v>
       </c>
       <c r="D386">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="387">
@@ -7339,7 +7339,7 @@
         <v>2</v>
       </c>
       <c r="D388">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="389">
@@ -7465,7 +7465,7 @@
         <v>2</v>
       </c>
       <c r="D395">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="396">
@@ -7483,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="D396">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="397">
@@ -7519,7 +7519,7 @@
         <v>2</v>
       </c>
       <c r="D398">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="399">
@@ -7591,7 +7591,7 @@
         <v>2</v>
       </c>
       <c r="D402">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="403">
@@ -7699,7 +7699,7 @@
         <v>2</v>
       </c>
       <c r="D408">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="409">
@@ -7789,7 +7789,7 @@
         <v>2</v>
       </c>
       <c r="D413">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="414">
@@ -8005,7 +8005,7 @@
         <v>2</v>
       </c>
       <c r="D425">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="426">
@@ -8059,7 +8059,7 @@
         <v>2</v>
       </c>
       <c r="D428">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="429">
@@ -8149,7 +8149,7 @@
         <v>2</v>
       </c>
       <c r="D433">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="434">
@@ -8275,7 +8275,7 @@
         <v>2</v>
       </c>
       <c r="D440">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="441">
@@ -8347,7 +8347,7 @@
         <v>2</v>
       </c>
       <c r="D444">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="445">
@@ -8383,7 +8383,7 @@
         <v>2</v>
       </c>
       <c r="D446">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="447">
@@ -8401,7 +8401,7 @@
         <v>2</v>
       </c>
       <c r="D447">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="448">
@@ -8707,7 +8707,7 @@
         <v>2</v>
       </c>
       <c r="D464">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="465">
@@ -8851,7 +8851,7 @@
         <v>2</v>
       </c>
       <c r="D472">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="473">
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="D479">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="480">
@@ -8995,7 +8995,7 @@
         <v>2</v>
       </c>
       <c r="D480">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="481">
@@ -9157,7 +9157,7 @@
         <v>2</v>
       </c>
       <c r="D489">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="490">
@@ -9409,7 +9409,7 @@
         <v>2</v>
       </c>
       <c r="D503">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="504">
@@ -9499,7 +9499,7 @@
         <v>2</v>
       </c>
       <c r="D508">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="509">
@@ -9535,7 +9535,7 @@
         <v>2</v>
       </c>
       <c r="D510">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="511">
@@ -9589,7 +9589,7 @@
         <v>2</v>
       </c>
       <c r="D513">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="514">
@@ -9661,7 +9661,7 @@
         <v>2</v>
       </c>
       <c r="D517">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="518">
@@ -10399,7 +10399,7 @@
         <v>2</v>
       </c>
       <c r="D558">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="559">
@@ -10831,7 +10831,7 @@
         <v>2</v>
       </c>
       <c r="D582">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="583">
@@ -11011,7 +11011,7 @@
         <v>2</v>
       </c>
       <c r="D592">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="593">
@@ -11029,7 +11029,7 @@
         <v>2</v>
       </c>
       <c r="D593">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="594">
@@ -11101,7 +11101,7 @@
         <v>2</v>
       </c>
       <c r="D597">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="598">
@@ -11173,7 +11173,7 @@
         <v>2</v>
       </c>
       <c r="D601">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="602">
@@ -11497,7 +11497,7 @@
         <v>2</v>
       </c>
       <c r="D619">
-        <v>0.0009250693802035153</v>
+        <v>0.0009250693802035152</v>
       </c>
     </row>
     <row r="620">
